--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 00:30:23</t>
+          <t>2026-05-31 02:49:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 02:49:46</t>
+          <t>2026-05-31 05:09:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 05:09:01</t>
+          <t>2026-05-31 07:27:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 07:27:48</t>
+          <t>2026-05-31 09:46:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 09:46:48</t>
+          <t>2026-05-31 12:02:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 12:02:48</t>
+          <t>2026-05-31 14:16:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -860,227 +860,227 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
         <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>
@@ -1123,34 +1123,34 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1273,68 +1273,68 @@
         <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 14:16:41</t>
+          <t>2026-05-31 16:28:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -896,7 +896,7 @@
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1150,7 +1150,7 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 16:28:45</t>
+          <t>2026-05-31 18:38:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1.24</v>
@@ -896,7 +896,7 @@
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 18:38:16</t>
+          <t>2026-05-31 20:47:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -1150,7 +1150,7 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 20:47:06</t>
+          <t>2026-05-31 22:55:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,261 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-31 22:55:02</t>
+          <t>2026-06-01 01:02:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medelli</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-01 01:02:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J3" t="n">
         <v>1.09</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>
@@ -1368,22 +1368,22 @@
         <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I4" t="n">
         <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1395,7 +1395,7 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>2.06</v>
@@ -1410,13 +1410,13 @@
         <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V4" t="n">
         <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
@@ -1470,7 +1470,7 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP4" t="n">
         <v>9.800000000000001</v>
@@ -1527,16 +1527,16 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1557,22 +1557,22 @@
         <v>7</v>
       </c>
       <c r="BR4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS4" t="n">
         <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
         <v>4.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>40</v>
@@ -1581,14 +1581,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA4" t="n">
         <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 01:02:48</t>
+          <t>2026-06-01 03:10:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J2" t="n">
         <v>1.04</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J3" t="n">
         <v>1.09</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
         <v>1.16</v>
@@ -1150,7 +1150,7 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
         <v>2.82</v>
@@ -1374,7 +1374,7 @@
         <v>2.88</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
@@ -1395,7 +1395,7 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
         <v>2.06</v>
@@ -1413,7 +1413,7 @@
         <v>2.04</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
         <v>1.55</v>
@@ -1527,25 +1527,25 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO4" t="n">
         <v>4.4</v>
@@ -1554,10 +1554,10 @@
         <v>22</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS4" t="n">
         <v>8</v>
@@ -1566,10 +1566,10 @@
         <v>6.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW4" t="n">
         <v>7.2</v>
@@ -1578,17 +1578,17 @@
         <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA4" t="n">
         <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 03:10:36</t>
+          <t>2026-06-01 05:18:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,33 +843,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>JJK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>VJS</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -878,25 +878,25 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.24</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -905,10 +905,10 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
@@ -1097,60 +1097,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="G3" t="n">
         <v>970</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="I3" t="n">
         <v>970</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1159,10 +1159,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,261 +1334,1023 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 05:18:35</t>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Swedish Division 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Assyriska FF</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Enkopings SK</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>970</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I4" t="n">
+        <v>970</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K4" t="n">
+        <v>950</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-01 07:26:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Belouizdad</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-01 07:26:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Union Brescia</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ascoli</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>950</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-01 07:26:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Atletico Nacional Medelli</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="F7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.25</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="T7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.46</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-01 05:18:35</t>
+      <c r="W7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-01 07:26:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,237 +857,237 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>1.16</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>RoPS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>OLS</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L3" t="n">
         <v>1.22</v>
       </c>
-      <c r="G3" t="n">
-        <v>970</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I3" t="n">
-        <v>970</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X3" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
@@ -1351,61 +1351,61 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.57</v>
       </c>
       <c r="G4" t="n">
         <v>970</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="I4" t="n">
         <v>970</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="R4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S4" t="n">
         <v>1.25</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.15</v>
-      </c>
       <c r="T4" t="n">
         <v>1.01</v>
       </c>
@@ -1413,10 +1413,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,33 +1605,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1640,25 +1640,25 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.24</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,117 +1859,117 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1978,40 +1978,40 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
         <v>1.03</v>
@@ -2035,322 +2035,576 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 07:26:54</t>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Italian Serie C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Union Brescia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ascoli</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:35:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Atletico Nacional Medelli</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="F8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H8" t="n">
         <v>2.92</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>3.3</v>
       </c>
-      <c r="J7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.04</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.02</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V8" t="n">
         <v>1.46</v>
       </c>
-      <c r="W7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-01 07:26:54</t>
+      <c r="W8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:35:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -881,7 +881,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
@@ -893,10 +893,10 @@
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T2" t="n">
         <v>1.51</v>
@@ -905,10 +905,10 @@
         <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
@@ -917,10 +917,10 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
         <v>970</v>
@@ -932,10 +932,10 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -944,16 +944,16 @@
         <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM2" t="n">
         <v>65</v>
@@ -962,125 +962,125 @@
         <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR2" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>19</v>
+        <v>4.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BF2" t="n">
         <v>4</v>
       </c>
       <c r="BG2" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.69</v>
+        <v>7</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.81</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -1135,22 +1135,22 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.17</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>1.52</v>
@@ -1159,22 +1159,22 @@
         <v>2.66</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
       </c>
       <c r="Y3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
         <v>18.5</v>
@@ -1183,10 +1183,10 @@
         <v>13</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
@@ -1198,13 +1198,13 @@
         <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL3" t="n">
         <v>32</v>
@@ -1213,22 +1213,22 @@
         <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1237,13 +1237,13 @@
         <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
         <v>8.4</v>
@@ -1252,25 +1252,25 @@
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
         <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1282,59 +1282,59 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
         <v>6.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BW3" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>28</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>970</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.61</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>970</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.09</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>970</v>
+        <v>2.82</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>2.58</v>
       </c>
       <c r="I5" t="n">
-        <v>970</v>
+        <v>3.35</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>2.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>1.15</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -1873,166 +1873,166 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X6" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX6" t="n">
         <v>4.3</v>
       </c>
-      <c r="G6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH6" t="n">
         <v>2.94</v>
@@ -2044,25 +2044,25 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.26</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2071,32 +2071,32 @@
         <v>9</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.47</v>
@@ -2151,34 +2151,34 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2187,106 +2187,106 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
         <v>60</v>
       </c>
-      <c r="AL7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>75</v>
-      </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AR7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY7" t="n">
         <v>3.55</v>
       </c>
-      <c r="AS7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW7" t="n">
+      <c r="AZ7" t="n">
         <v>3.95</v>
       </c>
-      <c r="AX7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BA7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
         <v>4.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
         <v>4.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>
@@ -2384,10 +2384,10 @@
         <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>3.3</v>
@@ -2396,7 +2396,7 @@
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.43</v>
@@ -2426,19 +2426,19 @@
         <v>1.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
         <v>25</v>
@@ -2450,19 +2450,19 @@
         <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -2474,31 +2474,31 @@
         <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>130</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
         <v>7.6</v>
@@ -2510,37 +2510,37 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.5</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH8" t="n">
         <v>3.3</v>
@@ -2552,16 +2552,16 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
         <v>4.3</v>
@@ -2570,41 +2570,41 @@
         <v>21</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR8" t="n">
         <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
         <v>27</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>42</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>34</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 09:35:19</t>
+          <t>2026-06-01 11:43:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -887,16 +887,16 @@
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="T2" t="n">
         <v>1.51</v>
@@ -905,10 +905,10 @@
         <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
@@ -920,10 +920,10 @@
         <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
@@ -932,10 +932,10 @@
         <v>970</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -950,10 +950,10 @@
         <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
         <v>65</v>
@@ -962,22 +962,22 @@
         <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
         <v>7.6</v>
@@ -986,37 +986,37 @@
         <v>9.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>16.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
@@ -1028,19 +1028,19 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1052,35 +1052,35 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.2</v>
@@ -1126,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.22</v>
@@ -1159,10 +1159,10 @@
         <v>2.66</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
         <v>34</v>
@@ -1222,7 +1222,7 @@
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
@@ -1261,16 +1261,16 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="BE3" t="n">
         <v>4</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="n">
         <v>4.7</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1368,16 +1368,16 @@
         <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="n">
         <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
@@ -1389,19 +1389,19 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.52</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.51</v>
       </c>
       <c r="S4" t="n">
         <v>2.28</v>
@@ -1413,7 +1413,7 @@
         <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
@@ -1422,7 +1422,7 @@
         <v>28</v>
       </c>
       <c r="Y4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
         <v>44</v>
@@ -1431,7 +1431,7 @@
         <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC4" t="n">
         <v>12</v>
@@ -1446,7 +1446,7 @@
         <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
@@ -1473,58 +1473,58 @@
         <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AR4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB4" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BC4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG4" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.9</v>
       </c>
       <c r="BH4" t="n">
         <v>4.4</v>
@@ -1536,7 +1536,7 @@
         <v>9.6</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="H5" t="n">
         <v>2.58</v>
@@ -1631,7 +1631,7 @@
         <v>3.35</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>4.5</v>
@@ -1643,22 +1643,22 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
         <v>1.5</v>
@@ -1670,13 +1670,13 @@
         <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
         <v>28</v>
@@ -1685,10 +1685,10 @@
         <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1703,19 +1703,19 @@
         <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
         <v>70</v>
@@ -1724,61 +1724,61 @@
         <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AS5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG5" t="n">
         <v>3.95</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>3.5</v>
       </c>
       <c r="BH5" t="n">
         <v>4.7</v>
@@ -1820,7 +1820,7 @@
         <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
         <v>20</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="I6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
@@ -1897,7 +1897,7 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
@@ -1912,10 +1912,10 @@
         <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U6" t="n">
         <v>1.62</v>
@@ -1924,19 +1924,19 @@
         <v>2.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
@@ -1945,16 +1945,16 @@
         <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH6" t="n">
         <v>44</v>
@@ -1966,7 +1966,7 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1981,58 +1981,58 @@
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU6" t="n">
         <v>3.8</v>
       </c>
-      <c r="AU6" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AV6" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG6" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.7</v>
       </c>
       <c r="BH6" t="n">
         <v>2.94</v>
@@ -2074,7 +2074,7 @@
         <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
@@ -2127,43 +2127,43 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
         <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="n">
         <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K7" t="n">
         <v>3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
         <v>2.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
         <v>5.5</v>
@@ -2196,7 +2196,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
         <v>970</v>
@@ -2214,10 +2214,10 @@
         <v>32</v>
       </c>
       <c r="AI7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
         <v>55</v>
@@ -2232,62 +2232,62 @@
         <v>60</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
         <v>4.1</v>
       </c>
       <c r="BC7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>4.1</v>
       </c>
-      <c r="BG7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH7" t="n">
         <v>1000</v>
       </c>
@@ -2350,261 +2350,515 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 11:43:58</t>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Deportivo Merlo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:52:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Atletico Nacional Medelli</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>2.56</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>2.68</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>3.3</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>3.25</v>
       </c>
-      <c r="K8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L9" t="n">
         <v>1.43</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>1.08</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N9" t="n">
         <v>3.25</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="O9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.04</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="V9" t="n">
         <v>1.44</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>1.6</v>
       </c>
-      <c r="X8" t="n">
+      <c r="X9" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y9" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="Z9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA9" t="n">
         <v>65</v>
       </c>
-      <c r="AB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AD9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE9" t="n">
         <v>46</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AF9" t="n">
         <v>18.5</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="BA9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP9" t="n">
         <v>21</v>
       </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK8" t="n">
+      <c r="BQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>34</v>
       </c>
-      <c r="AL8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA8" t="n">
+      <c r="CA9" t="n">
         <v>8</v>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-01 11:43:58</t>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:52:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -878,7 +878,7 @@
         <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
         <v>5.3</v>
@@ -887,13 +887,13 @@
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
         <v>2.36</v>
@@ -905,10 +905,10 @@
         <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
@@ -917,25 +917,25 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -950,7 +950,7 @@
         <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
         <v>34</v>
@@ -965,31 +965,31 @@
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>17</v>
-      </c>
       <c r="AX2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
         <v>4</v>
@@ -998,25 +998,25 @@
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BH2" t="n">
         <v>4.6</v>
@@ -1028,37 +1028,37 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
         <v>2.2</v>
@@ -1246,7 +1246,7 @@
         <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
         <v>11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -1365,64 +1365,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
         <v>44</v>
@@ -1440,155 +1440,155 @@
         <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>26</v>
       </c>
       <c r="AK4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD4" t="n">
         <v>22</v>
       </c>
-      <c r="AL4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP4" t="n">
+      <c r="BE4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BH4" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE4" t="n">
+      <c r="BI4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
         <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1685,10 +1685,10 @@
         <v>50</v>
       </c>
       <c r="AB5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1706,7 +1706,7 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
@@ -1727,58 +1727,58 @@
         <v>17</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AY5" t="n">
         <v>4</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS5" t="n">
+      <c r="AZ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA5" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="BB5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4</v>
       </c>
-      <c r="AU5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BG5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="n">
         <v>4.7</v>
@@ -1790,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV5" t="n">
         <v>20</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="I6" t="n">
         <v>1.8</v>
@@ -1888,7 +1888,7 @@
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
@@ -1897,52 +1897,52 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P6" t="n">
         <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
         <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
         <v>2.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,13 +1951,13 @@
         <v>26</v>
       </c>
       <c r="AF6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
@@ -1966,10 +1966,10 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL6" t="n">
         <v>160</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
@@ -1984,55 +1984,55 @@
         <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AW6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.2</v>
       </c>
       <c r="BH6" t="n">
         <v>2.94</v>
@@ -2074,7 +2074,7 @@
         <v>4.3</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -2172,13 +2172,13 @@
         <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2187,10 +2187,10 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -2202,7 +2202,7 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF7" t="n">
         <v>970</v>
@@ -2211,7 +2211,7 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -2220,73 +2220,73 @@
         <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BA7" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BC7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE7" t="n">
         <v>4</v>
       </c>
-      <c r="BD7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G9" t="n">
         <v>2.68</v>
@@ -2644,7 +2644,7 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
         <v>3.25</v>
@@ -2683,64 +2683,64 @@
         <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF9" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
         <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP9" t="n">
         <v>9.6</v>
@@ -2752,7 +2752,7 @@
         <v>16.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>7.4</v>
@@ -2764,7 +2764,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2776,25 +2776,25 @@
         <v>13.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.9</v>
+        <v>38</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BF9" t="n">
         <v>19.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="n">
         <v>3.3</v>
@@ -2818,7 +2818,7 @@
         <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
         <v>21</v>
@@ -2836,7 +2836,7 @@
         <v>6.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>27</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 13:52:40</t>
+          <t>2026-06-01 16:01:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,13 +860,13 @@
         <v>2.76</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
@@ -893,10 +893,10 @@
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
         <v>1.51</v>
@@ -908,10 +908,10 @@
         <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
@@ -923,13 +923,13 @@
         <v>38</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="n">
         <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>26</v>
@@ -941,7 +941,7 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI2" t="n">
         <v>34</v>
@@ -965,52 +965,52 @@
         <v>970</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
@@ -1028,13 +1028,13 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1046,16 +1046,16 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
         <v>4.6</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
         <v>3.2</v>
@@ -1123,52 +1123,52 @@
         <v>3.55</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
         <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U3" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
         <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
         <v>36</v>
@@ -1177,10 +1177,10 @@
         <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>18.5</v>
@@ -1228,7 +1228,7 @@
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1240,19 +1240,19 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1261,10 +1261,10 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BE3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
         <v>8.4</v>
@@ -1273,25 +1273,25 @@
         <v>17.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
         <v>4.2</v>
@@ -1300,48 +1300,48 @@
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,244 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>SV Grodig</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>TSV Neumarkt</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.82</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.05</v>
       </c>
-      <c r="N4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="BG4" t="n">
         <v>1.25</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BH4" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>2.72</v>
+        <v>1.99</v>
       </c>
       <c r="H5" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.24</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL5" t="n">
         <v>38</v>
       </c>
-      <c r="AK5" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>32</v>
-      </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS5" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AT5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="BF5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4</v>
       </c>
-      <c r="AW5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH5" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BI5" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
         <v>9</v>
       </c>
-      <c r="BK5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>6</v>
-      </c>
       <c r="BX5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BZ5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.6</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>2.72</v>
       </c>
       <c r="H6" t="n">
-        <v>1.64</v>
+        <v>2.58</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="J6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X6" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU6" t="n">
         <v>3.55</v>
       </c>
-      <c r="K6" t="n">
+      <c r="AV6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA6" t="n">
         <v>4.7</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="BB6" t="n">
         <v>4.7</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X6" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="BC6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>9</v>
       </c>
-      <c r="AA6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AS6" t="n">
+      <c r="BK6" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.26</v>
+        <v>7.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS6" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BT6" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BU6" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY6" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.78</v>
+        <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>1.85</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.54</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.49</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA7" t="n">
         <v>970</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>70</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
       </c>
       <c r="AC7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO7" t="n">
         <v>970</v>
       </c>
-      <c r="AD7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>70</v>
-      </c>
       <c r="AP7" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY7" t="n">
         <v>4.1</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AZ7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU7" t="n">
         <v>3.85</v>
       </c>
-      <c r="AX7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>8.6</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL8" t="n">
         <v>75</v>
       </c>
-      <c r="AF8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>90</v>
-      </c>
       <c r="AM8" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="AN8" t="n">
         <v>60</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AQ8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT8" t="n">
         <v>3.5</v>
       </c>
-      <c r="AR8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AU8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="AX8" t="n">
         <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 16:01:23</t>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,244 +2621,498 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medelli</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="G9" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
       </c>
       <c r="I9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.25</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.43</v>
       </c>
-      <c r="M9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.78</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" t="n">
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AJ9" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>5.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>19.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="BN9" t="n">
         <v>5.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:09:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Junior FC Barranquilla</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medelli</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP10" t="n">
         <v>21</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BQ10" t="n">
         <v>7</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="BR10" t="n">
         <v>36</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="BS10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="BT10" t="n">
         <v>6.4</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="BU10" t="n">
         <v>5.3</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="BV10" t="n">
         <v>27</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="BW10" t="n">
         <v>7.6</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="BX10" t="n">
         <v>42</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="BY10" t="n">
         <v>8.4</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="BZ10" t="n">
         <v>34</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CA10" t="n">
         <v>8</v>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:01:23</t>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:09:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -863,16 +863,16 @@
         <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J2" t="n">
         <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
@@ -884,10 +884,10 @@
         <v>5.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
@@ -899,7 +899,7 @@
         <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
         <v>2.56</v>
@@ -908,109 +908,109 @@
         <v>1.64</v>
       </c>
       <c r="W2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
         <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AH2" t="n">
         <v>17.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1052,7 +1052,7 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
         <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
@@ -1147,7 +1147,7 @@
         <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S3" t="n">
         <v>2.36</v>
@@ -1156,13 +1156,13 @@
         <v>1.53</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V3" t="n">
         <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
         <v>32</v>
@@ -1174,7 +1174,7 @@
         <v>36</v>
       </c>
       <c r="AA3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
         <v>18</v>
@@ -1210,7 +1210,7 @@
         <v>32</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN3" t="n">
         <v>11.5</v>
@@ -1222,13 +1222,13 @@
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
         <v>11</v>
@@ -1240,7 +1240,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
         <v>12.5</v>
@@ -1252,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1261,10 +1261,10 @@
         <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
         <v>8.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="G4" t="n">
         <v>12</v>
@@ -1374,22 +1374,22 @@
         <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K4" t="n">
+        <v>950</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
         <v>1.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.08</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.05</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
         <v>23</v>
@@ -1682,10 +1682,10 @@
         <v>44</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC5" t="n">
         <v>12</v>
@@ -1694,7 +1694,7 @@
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
         <v>15.5</v>
@@ -1706,85 +1706,85 @@
         <v>22</v>
       </c>
       <c r="AI5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>65</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>26</v>
-      </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>4</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BA5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF5" t="n">
         <v>3.4</v>
       </c>
-      <c r="AY5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="n">
         <v>3.95</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="Q6" t="n">
         <v>1.53</v>
@@ -1915,28 +1915,28 @@
         <v>2.32</v>
       </c>
       <c r="T6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.58</v>
       </c>
       <c r="X6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
         <v>18.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
         <v>17</v>
@@ -1945,16 +1945,16 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
         <v>16</v>
@@ -1966,73 +1966,73 @@
         <v>38</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
         <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AO6" t="n">
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF6" t="n">
         <v>5</v>
       </c>
-      <c r="BF6" t="n">
-        <v>4</v>
-      </c>
       <c r="BG6" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH6" t="n">
         <v>4.7</v>
@@ -2044,7 +2044,7 @@
         <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.46</v>
@@ -2151,206 +2151,206 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>90</v>
       </c>
       <c r="Y7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
         <v>7.2</v>
       </c>
-      <c r="Z7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>190</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.56</v>
@@ -2411,16 +2411,16 @@
         <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T8" t="n">
         <v>2.06</v>
@@ -2429,118 +2429,118 @@
         <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
         <v>970</v>
       </c>
       <c r="AA8" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
         <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AG8" t="n">
         <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>500</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.65</v>
+        <v>5.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.65</v>
+        <v>5.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="P9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
         <v>1.66</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB9" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="BC9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN9" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BO9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU9" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4</v>
-      </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
         <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
         <v>14</v>
@@ -3018,7 +3018,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -3030,13 +3030,13 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
         <v>7.2</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 18:09:04</t>
+          <t>2026-06-01 20:16:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G2" t="n">
         <v>3.15</v>
@@ -872,7 +872,7 @@
         <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
@@ -881,28 +881,28 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
         <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V2" t="n">
         <v>1.64</v>
@@ -917,19 +917,19 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -941,7 +941,7 @@
         <v>24</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -974,7 +974,7 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -989,7 +989,7 @@
         <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
         <v>7.6</v>
@@ -998,10 +998,10 @@
         <v>11</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
         <v>14.5</v>
@@ -1010,7 +1010,7 @@
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
@@ -1058,7 +1058,7 @@
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
         <v>2.24</v>
@@ -1120,13 +1120,13 @@
         <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.23</v>
@@ -1153,13 +1153,13 @@
         <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
         <v>2.58</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
         <v>1.81</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>12</v>
@@ -1398,7 +1398,7 @@
         <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
@@ -1410,7 +1410,7 @@
         <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1521,7 +1521,7 @@
         <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
         <v>1.01</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>9</v>
@@ -1757,7 +1757,7 @@
         <v>5.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BA5" t="n">
         <v>4.1</v>
@@ -1766,7 +1766,7 @@
         <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
         <v>4.1</v>
@@ -1775,7 +1775,7 @@
         <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BG5" t="n">
         <v>4.5</v>
@@ -1784,7 +1784,7 @@
         <v>3.95</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -1897,19 +1897,19 @@
         <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>2.84</v>
+        <v>2.46</v>
       </c>
       <c r="Q6" t="n">
         <v>1.53</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
         <v>2.32</v>
@@ -1975,7 +1975,7 @@
         <v>60</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>17</v>
@@ -1984,55 +1984,55 @@
         <v>6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>6.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU6" t="n">
         <v>5.1</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY6" t="n">
         <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
         <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
         <v>5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH6" t="n">
         <v>4.7</v>
@@ -2044,7 +2044,7 @@
         <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -2127,76 +2127,76 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.61</v>
       </c>
-      <c r="I7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V7" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>21</v>
@@ -2205,91 +2205,91 @@
         <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AL7" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AM7" t="n">
-        <v>580</v>
+        <v>260</v>
       </c>
       <c r="AN7" t="n">
         <v>700</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>9.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.15</v>
+        <v>9.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="BI7" t="n">
         <v>2.46</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.36</v>
+        <v>1.48</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="BT7" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G8" t="n">
         <v>2.96</v>
       </c>
       <c r="H8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I8" t="n">
         <v>3.05</v>
       </c>
-      <c r="I8" t="n">
-        <v>3.2</v>
-      </c>
       <c r="J8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.56</v>
@@ -2423,13 +2423,13 @@
         <v>5.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
         <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
         <v>1.51</v>
@@ -2447,7 +2447,7 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>11.5</v>
@@ -2459,10 +2459,10 @@
         <v>500</v>
       </c>
       <c r="AF8" t="n">
-        <v>38</v>
+        <v>17.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AH8" t="n">
         <v>500</v>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
         <v>4.9</v>
@@ -2510,7 +2510,7 @@
         <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX8" t="n">
         <v>7.6</v>
@@ -2519,92 +2519,92 @@
         <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC8" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC8" t="n">
-        <v>5</v>
-      </c>
       <c r="BD8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
         <v>6</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
         <v>3.45</v>
@@ -2647,19 +2647,19 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
         <v>1.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O9" t="n">
         <v>1.65</v>
@@ -2671,22 +2671,22 @@
         <v>2.98</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S9" t="n">
         <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V9" t="n">
         <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
         <v>7.4</v>
@@ -2704,7 +2704,7 @@
         <v>7.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
         <v>18</v>
@@ -2719,7 +2719,7 @@
         <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2749,52 +2749,52 @@
         <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AU9" t="n">
         <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE9" t="n">
         <v>9.6</v>
       </c>
-      <c r="BE9" t="n">
-        <v>10</v>
-      </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="n">
         <v>2.54</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
         <v>3.25</v>
@@ -2913,7 +2913,7 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.37</v>
@@ -2931,13 +2931,13 @@
         <v>3.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
         <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
         <v>1.59</v>
@@ -2946,7 +2946,7 @@
         <v>14</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
         <v>23</v>
@@ -2961,13 +2961,13 @@
         <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
         <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
@@ -3006,7 +3006,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -3021,7 +3021,7 @@
         <v>7.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
@@ -3033,22 +3033,22 @@
         <v>7.4</v>
       </c>
       <c r="BB10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC10" t="n">
         <v>7</v>
       </c>
-      <c r="BC10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
         <v>19.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="n">
         <v>3.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 20:16:41</t>
+          <t>2026-06-01 22:23:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,55 +857,55 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G2" t="n">
         <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="W2" t="n">
         <v>1.47</v>
@@ -920,13 +920,13 @@
         <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
         <v>32</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
@@ -962,7 +962,7 @@
         <v>970</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
@@ -974,10 +974,10 @@
         <v>14.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
         <v>5.6</v>
@@ -986,22 +986,22 @@
         <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY2" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>14.5</v>
@@ -1010,7 +1010,7 @@
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
         <v>13</v>
@@ -1019,10 +1019,10 @@
         <v>9.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
         <v>3.2</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
@@ -1135,31 +1135,31 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
         <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>1.54</v>
       </c>
       <c r="U3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
         <v>1.81</v>
@@ -1183,7 +1183,7 @@
         <v>12.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>17.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BI3" t="n">
         <v>3.5</v>
@@ -1315,26 +1315,26 @@
         <v>5.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY3" t="n">
         <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="G4" t="n">
         <v>12</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
         <v>4.9</v>
@@ -1643,34 +1643,34 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
         <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X5" t="n">
         <v>28</v>
@@ -1679,7 +1679,7 @@
         <v>23</v>
       </c>
       <c r="Z5" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
@@ -1688,10 +1688,10 @@
         <v>27</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
@@ -1700,7 +1700,7 @@
         <v>15.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
@@ -1712,31 +1712,31 @@
         <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
         <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="AQ5" t="n">
         <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
         <v>5.8</v>
@@ -1745,10 +1745,10 @@
         <v>5.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
         <v>6.4</v>
@@ -1760,31 +1760,31 @@
         <v>10.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BC5" t="n">
         <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BN5" t="n">
         <v>4.9</v>
@@ -1817,32 +1817,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>2.72</v>
       </c>
       <c r="H6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
         <v>3.05</v>
@@ -2044,7 +2044,7 @@
         <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>4.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
         <v>1.83</v>
       </c>
       <c r="I7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.51</v>
@@ -2163,7 +2163,7 @@
         <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
         <v>5.1</v>
@@ -2172,40 +2172,40 @@
         <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
         <v>10</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AA7" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AB7" t="n">
         <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="AG7" t="n">
         <v>28</v>
@@ -2232,25 +2232,25 @@
         <v>700</v>
       </c>
       <c r="AO7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
         <v>9.6</v>
@@ -2262,31 +2262,31 @@
         <v>29</v>
       </c>
       <c r="AY7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="BA7" t="n">
         <v>38</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH7" t="n">
         <v>2.96</v>
@@ -2298,7 +2298,7 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,25 +2310,25 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="BT7" t="n">
         <v>4.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.05</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
         <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
         <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>500</v>
       </c>
       <c r="Z8" t="n">
         <v>970</v>
@@ -2465,7 +2465,7 @@
         <v>26</v>
       </c>
       <c r="AH8" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
@@ -2480,7 +2480,7 @@
         <v>500</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>500</v>
@@ -2498,7 +2498,7 @@
         <v>9</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>4.9</v>
@@ -2510,7 +2510,7 @@
         <v>7.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
         <v>7.6</v>
@@ -2519,92 +2519,92 @@
         <v>7.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BA8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC8" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD8" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="BF8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
         <v>6</v>
       </c>
-      <c r="BG8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
         <v>2.76</v>
@@ -2662,34 +2662,34 @@
         <v>2.26</v>
       </c>
       <c r="O9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
         <v>1.65</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
         <v>9.4</v>
@@ -2701,7 +2701,7 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" t="n">
         <v>7.6</v>
@@ -2725,7 +2725,7 @@
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>500</v>
@@ -2746,55 +2746,55 @@
         <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB9" t="n">
         <v>7</v>
       </c>
-      <c r="AR9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8</v>
-      </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH9" t="n">
         <v>2.54</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
         <v>2.68</v>
@@ -2913,22 +2913,22 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
         <v>1.8</v>
@@ -2964,7 +2964,7 @@
         <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF10" t="n">
         <v>18</v>
@@ -2973,7 +2973,7 @@
         <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
         <v>55</v>
@@ -2994,7 +2994,7 @@
         <v>27</v>
       </c>
       <c r="AO10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP10" t="n">
         <v>9.6</v>
@@ -3006,7 +3006,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>7.4</v>
@@ -3018,7 +3018,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>14.5</v>
@@ -3030,25 +3030,25 @@
         <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC10" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC10" t="n">
-        <v>7</v>
-      </c>
       <c r="BD10" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
         <v>19.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="n">
         <v>3.3</v>
@@ -3060,13 +3060,13 @@
         <v>10.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>5.6</v>
@@ -3102,17 +3102,17 @@
         <v>42</v>
       </c>
       <c r="BY10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA10" t="n">
         <v>8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-01 22:23:10</t>
+          <t>2026-06-02 00:29:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
         <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -884,52 +884,52 @@
         <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
         <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
         <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V2" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
         <v>32</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -941,7 +941,7 @@
         <v>24</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>500</v>
@@ -959,64 +959,64 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>12.5</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW2" t="n">
         <v>10.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE2" t="n">
         <v>23</v>
       </c>
-      <c r="BE2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH2" t="n">
         <v>4.7</v>
@@ -1028,7 +1028,7 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1043,7 +1043,7 @@
         <v>5.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
         <v>6.6</v>
@@ -1061,10 +1061,10 @@
         <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1073,14 +1073,14 @@
         <v>6.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA2" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -1111,166 +1111,166 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U3" t="n">
         <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
         <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
         <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AM3" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>23</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
         <v>4.6</v>
@@ -1282,59 +1282,59 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR3" t="n">
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3" t="n">
         <v>15</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
         <v>990</v>
       </c>
       <c r="J4" t="n">
-        <v>2.06</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="S4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1416,7 +1416,7 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>4.3</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1467,64 +1467,64 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1610,239 +1610,239 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>SK Austria Klagenfurt Amateure</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>Atus Ferlach</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>1.97</v>
+        <v>110</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>1.11</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
@@ -1859,138 +1859,138 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Rosengard</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Angelholms</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>1.81</v>
       </c>
       <c r="G6" t="n">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
         <v>4.6</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>1.24</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="P6" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="U6" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="X6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB6" t="n">
         <v>27</v>
       </c>
-      <c r="Y6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>17</v>
-      </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>5.8</v>
@@ -1999,111 +1999,111 @@
         <v>5.1</v>
       </c>
       <c r="AV6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK6" t="n">
         <v>5.4</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>6.2</v>
       </c>
-      <c r="AX6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BU6" t="n">
         <v>6</v>
       </c>
-      <c r="BD6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,251 +2113,251 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Assyriska FF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Enkopings SK</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.4</v>
+        <v>2.36</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>2.62</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG7" t="n">
         <v>13</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO7" t="n">
         <v>21</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>230</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>6</v>
       </c>
       <c r="AQ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX7" t="n">
         <v>5.9</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AY7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>7.8</v>
       </c>
-      <c r="AS7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BN7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR7" t="n">
         <v>28</v>
       </c>
-      <c r="BD7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
+      <c r="BS7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW7" t="n">
         <v>6</v>
       </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BX7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,251 +2367,251 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.78</v>
+        <v>4.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.92</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>9.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>500</v>
+        <v>6.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD8" t="n">
         <v>11</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE8" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB8" t="n">
+      <c r="BF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BT8" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG8" t="n">
+      <c r="BU8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
         <v>8</v>
       </c>
-      <c r="BH8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,93 +2621,93 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.4</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>500</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
@@ -2719,13 +2719,13 @@
         <v>26</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>500</v>
@@ -2734,7 +2734,7 @@
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>500</v>
@@ -2743,79 +2743,79 @@
         <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.6</v>
+        <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="BE9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BF9" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF9" t="n">
-        <v>7</v>
-      </c>
       <c r="BG9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="BJ9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
         <v>4.1</v>
@@ -2824,295 +2824,549 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>2.74</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.199999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>2.72</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>9.199999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.199999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 00:29:56</t>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Deportivo Merlo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X10" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>11</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-02 02:36:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>21:30:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Junior FC Barranquilla</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Atletico Nacional Medelli</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="F11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I11" t="n">
         <v>3.3</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>3.25</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>3.4</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="L11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.08</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH11" t="n">
         <v>3.3</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X10" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="BI11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ11" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="BK11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW11" t="n">
         <v>8</v>
       </c>
-      <c r="AD10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="BX11" t="n">
         <v>40</v>
       </c>
-      <c r="AF10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BY11" t="n">
         <v>9</v>
       </c>
-      <c r="AR10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD10" t="n">
+      <c r="BZ11" t="n">
         <v>32</v>
       </c>
-      <c r="BE10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>42</v>
-      </c>
-      <c r="BY10" t="n">
+      <c r="CA11" t="n">
         <v>8.6</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>8</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-02 00:29:56</t>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-02 02:36:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G2" t="n">
         <v>3.1</v>
@@ -881,28 +881,28 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U2" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="V2" t="n">
         <v>1.68</v>
@@ -914,10 +914,10 @@
         <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="n">
         <v>120</v>
@@ -929,70 +929,70 @@
         <v>10.5</v>
       </c>
       <c r="AD2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM2" t="n">
         <v>500</v>
       </c>
-      <c r="AE2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
       <c r="AN2" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
         <v>12.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AS2" t="n">
         <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>10.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>12</v>
@@ -1004,37 +1004,37 @@
         <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="BE2" t="n">
         <v>23</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BG2" t="n">
         <v>10</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
@@ -1043,44 +1043,44 @@
         <v>5.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>16.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1117,19 +1117,19 @@
         <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
         <v>3.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1138,7 +1138,7 @@
         <v>5.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
         <v>2.6</v>
@@ -1153,19 +1153,19 @@
         <v>2.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
         <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1183,13 +1183,13 @@
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
@@ -1198,7 +1198,7 @@
         <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -1213,25 +1213,25 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
@@ -1252,28 +1252,28 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
         <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI3" t="n">
         <v>3.5</v>
@@ -1282,31 +1282,31 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
         <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3" t="n">
         <v>7.2</v>
@@ -1318,23 +1318,23 @@
         <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
         <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>15</v>
       </c>
       <c r="CA3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1365,115 +1365,115 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>990</v>
+        <v>28</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="S4" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>2.22</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.2</v>
@@ -1485,10 +1485,10 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.02</v>
+        <v>1.84</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
@@ -1497,98 +1497,98 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1619,31 +1619,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.11</v>
@@ -1655,7 +1655,7 @@
         <v>1.11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>1.11</v>
@@ -1721,7 +1721,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1772,13 +1772,13 @@
         <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1873,61 +1873,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="X6" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="Y6" t="n">
         <v>950</v>
@@ -1942,7 +1942,7 @@
         <v>27</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,7 +1951,7 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
         <v>15</v>
@@ -1963,10 +1963,10 @@
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
         <v>500</v>
@@ -1975,46 +1975,46 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>5.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>10.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -2023,16 +2023,16 @@
         <v>9</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="BH6" t="n">
         <v>4</v>
@@ -2041,7 +2041,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK6" t="n">
         <v>5.4</v>
@@ -2053,16 +2053,16 @@
         <v>11</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2071,10 +2071,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2127,76 +2127,76 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="I7" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.57</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
         <v>44</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
@@ -2211,146 +2211,146 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS7" t="n">
         <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU7" t="n">
         <v>5.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
         <v>6.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG7" t="n">
         <v>5.5</v>
       </c>
-      <c r="BG7" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BH7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT7" t="n">
         <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV7" t="n">
         <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CA7" t="n">
         <v>6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G8" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="I8" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.58</v>
@@ -2405,7 +2405,7 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O8" t="n">
         <v>1.55</v>
@@ -2414,145 +2414,145 @@
         <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
         <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="V8" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB8" t="n">
         <v>13</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG8" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AH8" t="n">
         <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AL8" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AM8" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN8" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>11</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AY8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
         <v>48</v>
       </c>
       <c r="BB8" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BD8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BE8" t="n">
         <v>11.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,50 +2561,50 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>65</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>5.8</v>
       </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.05</v>
+        <v>8.6</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I9" t="n">
         <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
         <v>1.58</v>
@@ -2659,34 +2659,34 @@
         <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
         <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
         <v>18</v>
@@ -2698,10 +2698,10 @@
         <v>970</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
@@ -2713,10 +2713,10 @@
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>60</v>
@@ -2737,34 +2737,34 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5.2</v>
       </c>
       <c r="AR9" t="n">
         <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AT9" t="n">
         <v>5.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AX9" t="n">
         <v>7.6</v>
@@ -2773,34 +2773,34 @@
         <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="BB9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD9" t="n">
         <v>3.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3</v>
-      </c>
       <c r="BE9" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="BF9" t="n">
         <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
@@ -2812,10 +2812,10 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO9" t="n">
         <v>4.1</v>
@@ -2824,41 +2824,41 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.74</v>
+        <v>1.42</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.86</v>
+        <v>1.11</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.72</v>
+        <v>7.8</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2889,34 +2889,34 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N10" t="n">
         <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="P10" t="n">
         <v>1.42</v>
@@ -2931,25 +2931,25 @@
         <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
@@ -2961,7 +2961,7 @@
         <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2973,13 +2973,13 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2997,58 +2997,58 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.85</v>
+        <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.74</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="BH10" t="n">
         <v>2.54</v>
@@ -3075,7 +3075,7 @@
         <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ10" t="n">
         <v>8.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3143,127 +3143,127 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="G11" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="H11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>3.3</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
         <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
         <v>14</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
         <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
@@ -3272,43 +3272,43 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BH11" t="n">
         <v>3.3</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BJ11" t="n">
         <v>10</v>
@@ -3323,16 +3323,16 @@
         <v>10.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BO11" t="n">
         <v>4.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR11" t="n">
         <v>36</v>
@@ -3341,19 +3341,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BV11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY11" t="n">
         <v>9</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 02:36:39</t>
+          <t>2026-06-02 04:43:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,31 +857,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="I2" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
@@ -899,16 +899,16 @@
         <v>2.32</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
@@ -917,82 +917,82 @@
         <v>29</v>
       </c>
       <c r="Z2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
         <v>65</v>
       </c>
       <c r="AG2" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
         <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AS2" t="n">
         <v>21</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15</v>
-      </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>12</v>
@@ -1001,58 +1001,58 @@
         <v>14.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BF2" t="n">
         <v>10</v>
       </c>
       <c r="BG2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>6.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
@@ -1061,26 +1061,26 @@
         <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BZ2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
         <v>3.35</v>
@@ -1126,7 +1126,7 @@
         <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1135,37 +1135,37 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
         <v>1.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U3" t="n">
         <v>2.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1180,7 +1180,7 @@
         <v>15</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>15</v>
@@ -1195,10 +1195,10 @@
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -1219,16 +1219,16 @@
         <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
         <v>12.5</v>
@@ -1240,7 +1240,7 @@
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX3" t="n">
         <v>14.5</v>
@@ -1252,25 +1252,25 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
       </c>
       <c r="BD3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="n">
         <v>4.5</v>
@@ -1282,7 +1282,7 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1306,7 +1306,7 @@
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7.2</v>
@@ -1318,23 +1318,23 @@
         <v>24</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA3" t="n">
         <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="G4" t="n">
         <v>1.18</v>
       </c>
       <c r="H4" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="K4" t="n">
         <v>13.5</v>
@@ -1395,16 +1395,16 @@
         <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
         <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T4" t="n">
         <v>1.81</v>
@@ -1413,10 +1413,10 @@
         <v>1.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="X4" t="n">
         <v>95</v>
@@ -1473,7 +1473,7 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.2</v>
@@ -1488,7 +1488,7 @@
         <v>2.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
@@ -1497,25 +1497,25 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.86</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="BE4" t="n">
         <v>1.92</v>
@@ -1524,71 +1524,71 @@
         <v>1.96</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>14</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN4" t="n">
         <v>4.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP4" t="n">
         <v>6.4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BR4" t="n">
         <v>18</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>7.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>5</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -1625,19 +1625,19 @@
         <v>1.55</v>
       </c>
       <c r="H5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
@@ -1670,10 +1670,10 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1730,52 +1730,52 @@
         <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="BE5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.01</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG5" t="n">
         <v>1.55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="G6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1903,34 +1903,34 @@
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
         <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1939,10 +1939,10 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,10 +1951,10 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
         <v>60</v>
@@ -1969,7 +1969,7 @@
         <v>38</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1984,34 +1984,34 @@
         <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX6" t="n">
         <v>6.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
@@ -2020,31 +2020,31 @@
         <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
         <v>8</v>
       </c>
       <c r="BG6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,7 +2056,7 @@
         <v>4.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
         <v>12</v>
@@ -2068,13 +2068,13 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT6" t="n">
         <v>8.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
@@ -2086,7 +2086,7 @@
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H7" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.9</v>
@@ -2145,127 +2145,127 @@
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
         <v>1.58</v>
       </c>
       <c r="U7" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X7" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="n">
         <v>25</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>24</v>
       </c>
       <c r="AA7" t="n">
         <v>44</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ7" t="n">
         <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM7" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
         <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
         <v>5.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW7" t="n">
         <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BA7" t="n">
         <v>8.800000000000001</v>
@@ -2280,77 +2280,77 @@
         <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO7" t="n">
         <v>3.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BW7" t="n">
         <v>6</v>
       </c>
-      <c r="BR7" t="n">
+      <c r="BX7" t="n">
         <v>26</v>
       </c>
-      <c r="BS7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT7" t="n">
+      <c r="BY7" t="n">
         <v>6.6</v>
       </c>
-      <c r="BU7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="I8" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.58</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
         <v>2.68</v>
@@ -2411,82 +2411,82 @@
         <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.2</v>
       </c>
-      <c r="S8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AB8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
         <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AF8" t="n">
-        <v>36</v>
+        <v>230</v>
       </c>
       <c r="AG8" t="n">
         <v>24</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AK8" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL8" t="n">
         <v>700</v>
       </c>
       <c r="AM8" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AP8" t="n">
         <v>7.8</v>
@@ -2495,10 +2495,10 @@
         <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT8" t="n">
         <v>11</v>
@@ -2510,101 +2510,101 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>26</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BA8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG8" t="n">
         <v>18</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB8" t="n">
+      <c r="BH8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>970</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
         <v>11</v>
       </c>
-      <c r="BC8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD8" t="n">
+      <c r="BZ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA8" t="n">
         <v>11</v>
       </c>
-      <c r="BE8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>8.6</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -2635,28 +2635,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="L9" t="n">
         <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N9" t="n">
         <v>2.74</v>
@@ -2668,19 +2668,19 @@
         <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
         <v>1.49</v>
@@ -2689,10 +2689,10 @@
         <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>9.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
         <v>970</v>
@@ -2704,7 +2704,7 @@
         <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
         <v>500</v>
@@ -2725,7 +2725,7 @@
         <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
         <v>500</v>
@@ -2734,7 +2734,7 @@
         <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
         <v>600</v>
@@ -2743,58 +2743,58 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR9" t="n">
         <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV9" t="n">
         <v>7.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY9" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.15</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
         <v>7.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="n">
         <v>2.74</v>
@@ -2824,7 +2824,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.42</v>
+        <v>1.06</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -2889,58 +2889,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="M10" t="n">
         <v>1.17</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
         <v>7.2</v>
@@ -2955,10 +2955,10 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
         <v>30</v>
@@ -2967,19 +2967,19 @@
         <v>500</v>
       </c>
       <c r="AF10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG10" t="n">
         <v>15</v>
       </c>
-      <c r="AG10" t="n">
-        <v>26</v>
-      </c>
       <c r="AH10" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2997,28 +2997,28 @@
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU10" t="n">
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -3033,10 +3033,10 @@
         <v>9.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD10" t="n">
         <v>9.199999999999999</v>
@@ -3051,22 +3051,22 @@
         <v>9.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
         <v>5.3</v>
@@ -3075,7 +3075,7 @@
         <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
         <v>8.6</v>
@@ -3087,16 +3087,16 @@
         <v>10.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G11" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
@@ -3179,7 +3179,7 @@
         <v>2.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
         <v>3.95</v>
@@ -3188,16 +3188,16 @@
         <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
         <v>11.5</v>
@@ -3206,19 +3206,19 @@
         <v>19.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB11" t="n">
         <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
         <v>13.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF11" t="n">
         <v>21</v>
@@ -3236,7 +3236,7 @@
         <v>44</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
         <v>46</v>
@@ -3245,13 +3245,13 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO11" t="n">
         <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.4</v>
@@ -3263,10 +3263,10 @@
         <v>34</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
@@ -3275,7 +3275,7 @@
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
@@ -3284,22 +3284,22 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG11" t="n">
         <v>24</v>
@@ -3326,7 +3326,7 @@
         <v>6</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BP11" t="n">
         <v>23</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 04:43:26</t>
+          <t>2026-06-02 06:50:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
@@ -881,103 +881,103 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S2" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V2" t="n">
         <v>1.72</v>
       </c>
       <c r="W2" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
       </c>
       <c r="Y2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF2" t="n">
         <v>40</v>
       </c>
-      <c r="AF2" t="n">
-        <v>65</v>
-      </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO2" t="n">
         <v>11</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
         <v>8.800000000000001</v>
@@ -986,10 +986,10 @@
         <v>10</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>11.5</v>
@@ -998,28 +998,28 @@
         <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
         <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI2" t="n">
         <v>3.8</v>
@@ -1028,59 +1028,59 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU2" t="n">
         <v>5</v>
       </c>
       <c r="BV2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I3" t="n">
         <v>3.6</v>
@@ -1126,7 +1126,7 @@
         <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1135,37 +1135,37 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="Q3" t="n">
         <v>1.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
         <v>1.53</v>
       </c>
       <c r="U3" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="n">
         <v>21</v>
@@ -1174,7 +1174,7 @@
         <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
         <v>15</v>
@@ -1213,7 +1213,7 @@
         <v>160</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO3" t="n">
         <v>23</v>
@@ -1222,7 +1222,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR3" t="n">
         <v>15</v>
@@ -1231,7 +1231,7 @@
         <v>23</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
@@ -1282,59 +1282,59 @@
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BR3" t="n">
         <v>22</v>
       </c>
       <c r="BS3" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
         <v>7.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1368,112 +1368,112 @@
         <v>1.16</v>
       </c>
       <c r="G4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="K4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S4" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="X4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="Y4" t="n">
         <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AD4" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AE4" t="n">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
         <v>13</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>4.2</v>
@@ -1485,10 +1485,10 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV4" t="n">
         <v>4.2</v>
@@ -1497,43 +1497,43 @@
         <v>4.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>2.5</v>
       </c>
-      <c r="BE4" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="BG4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH4" t="n">
         <v>7.8</v>
       </c>
-      <c r="BH4" t="n">
-        <v>8</v>
-      </c>
       <c r="BI4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK4" t="n">
         <v>5.4</v>
@@ -1542,13 +1542,13 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP4" t="n">
         <v>6.4</v>
@@ -1557,13 +1557,13 @@
         <v>3.7</v>
       </c>
       <c r="BR4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS4" t="n">
         <v>5.9</v>
       </c>
       <c r="BT4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BU4" t="n">
         <v>6.2</v>
@@ -1575,20 +1575,20 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>1.55</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O5" t="n">
         <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,10 +1667,10 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="X5" t="n">
         <v>90</v>
@@ -1688,7 +1688,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1709,7 +1709,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1727,55 +1727,55 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AQ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
         <v>1.55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -1879,52 +1879,52 @@
         <v>1.81</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X6" t="n">
         <v>24</v>
@@ -1939,7 +1939,7 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
         <v>13.5</v>
@@ -1951,13 +1951,13 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
         <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1972,10 +1972,10 @@
         <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
@@ -1987,16 +1987,16 @@
         <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT6" t="n">
         <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
@@ -2005,7 +2005,7 @@
         <v>10.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
         <v>8.6</v>
@@ -2026,22 +2026,22 @@
         <v>16</v>
       </c>
       <c r="BE6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
         <v>5.5</v>
@@ -2059,7 +2059,7 @@
         <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BQ6" t="n">
         <v>6</v>
@@ -2071,32 +2071,32 @@
         <v>8</v>
       </c>
       <c r="BT6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2127,85 +2127,85 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="H7" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
         <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="T7" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB7" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
         <v>13.5</v>
@@ -2214,58 +2214,58 @@
         <v>15.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ7" t="n">
         <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>6</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
         <v>5.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
         <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA7" t="n">
         <v>8.800000000000001</v>
@@ -2274,31 +2274,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD7" t="n">
         <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH7" t="n">
         <v>5</v>
       </c>
-      <c r="BG7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BI7" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,19 +2307,19 @@
         <v>7.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
         <v>5.9</v>
       </c>
       <c r="BR7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS7" t="n">
         <v>6.4</v>
@@ -2328,29 +2328,29 @@
         <v>6.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BW7" t="n">
         <v>6</v>
       </c>
       <c r="BX7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY7" t="n">
         <v>6.6</v>
       </c>
       <c r="BZ7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2381,28 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="I8" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
         <v>2.68</v>
@@ -2414,187 +2414,187 @@
         <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
         <v>5.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AH8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AK8" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AL8" t="n">
         <v>700</v>
       </c>
       <c r="AM8" t="n">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX8" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AY8" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB8" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="BC8" t="n">
         <v>38</v>
       </c>
       <c r="BD8" t="n">
-        <v>55</v>
+        <v>16.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="BF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BV8" t="n">
         <v>13</v>
       </c>
-      <c r="BG8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BW8" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2635,31 +2635,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="I9" t="n">
         <v>3.05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
         <v>1.52</v>
@@ -2674,127 +2674,127 @@
         <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
         <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z9" t="n">
         <v>17.5</v>
       </c>
-      <c r="Z9" t="n">
-        <v>970</v>
-      </c>
       <c r="AA9" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AB9" t="n">
         <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AM9" t="n">
         <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BD9" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BH9" t="n">
         <v>2.74</v>
@@ -2812,53 +2812,53 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="BN9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.06</v>
+        <v>1.62</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -2889,61 +2889,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="L10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Y10" t="n">
         <v>9.4</v>
@@ -2955,13 +2955,13 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2970,10 +2970,10 @@
         <v>29</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
@@ -2991,34 +2991,34 @@
         <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU10" t="n">
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -3027,76 +3027,76 @@
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>12</v>
-      </c>
       <c r="BN10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO10" t="n">
         <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
         <v>7</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
@@ -3108,11 +3108,11 @@
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>
@@ -3143,52 +3143,52 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="G11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
         <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
         <v>3.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
@@ -3200,7 +3200,7 @@
         <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
         <v>19.5</v>
@@ -3224,7 +3224,7 @@
         <v>21</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>17.5</v>
@@ -3233,13 +3233,13 @@
         <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK11" t="n">
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -3251,7 +3251,7 @@
         <v>32</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.4</v>
@@ -3272,34 +3272,34 @@
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
         <v>36</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD11" t="n">
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11" t="n">
         <v>24</v>
@@ -3335,13 +3335,13 @@
         <v>7.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU11" t="n">
         <v>5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 06:50:15</t>
+          <t>2026-06-02 08:57:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,178 +857,178 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AG2" t="n">
         <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AJ2" t="n">
-        <v>280</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL2" t="n">
         <v>46</v>
       </c>
-      <c r="AL2" t="n">
-        <v>50</v>
-      </c>
       <c r="AM2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AP2" t="n">
         <v>13</v>
       </c>
       <c r="AQ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF2" t="n">
         <v>13.5</v>
       </c>
-      <c r="AR2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="BG2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
         <v>3.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,50 +1037,50 @@
         <v>50</v>
       </c>
       <c r="BN2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO2" t="n">
         <v>5.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS2" t="n">
         <v>8</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BW2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="CA2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>6.4</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.29</v>
@@ -1135,206 +1135,206 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="X3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AL3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AP3" t="n">
         <v>23</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>18</v>
-      </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AX3" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.5</v>
+        <v>29</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ3" t="n">
         <v>8.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BS3" t="n">
         <v>10</v>
       </c>
-      <c r="BR3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BT3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
         <v>9.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1365,118 +1365,118 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
         <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="S4" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="X4" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="Y4" t="n">
         <v>950</v>
       </c>
       <c r="Z4" t="n">
+        <v>260</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE4" t="n">
         <v>240</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>260</v>
-      </c>
       <c r="AF4" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
@@ -1485,55 +1485,55 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY4" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
         <v>2.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
         <v>5.4</v>
@@ -1542,53 +1542,53 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BP4" t="n">
         <v>6.4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT4" t="n">
         <v>21</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BX4" t="n">
-        <v>75</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>8</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="H5" t="n">
         <v>3.3</v>
@@ -1637,28 +1637,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.29</v>
+        <v>6.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1670,7 +1670,7 @@
         <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>90</v>
@@ -1685,10 +1685,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1697,10 +1697,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1712,10 +1712,10 @@
         <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1727,58 +1727,58 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.08</v>
+        <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -1873,64 +1873,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="G6" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
         <v>3.95</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="W6" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
         <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1942,7 +1942,7 @@
         <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,115 +1951,115 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO6" t="n">
         <v>600</v>
       </c>
       <c r="AP6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>9</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
         <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI6" t="n">
         <v>3.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP6" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BQ6" t="n">
         <v>6</v>
@@ -2068,35 +2068,35 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BU6" t="n">
         <v>9</v>
       </c>
-      <c r="BU6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2127,133 +2127,133 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="U7" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK7" t="n">
         <v>32</v>
       </c>
-      <c r="Y7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AL7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN7" t="n">
         <v>14</v>
       </c>
-      <c r="AE7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AO7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT7" t="n">
         <v>8.4</v>
       </c>
-      <c r="AT7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AU7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AW7" t="n">
         <v>7</v>
@@ -2265,40 +2265,40 @@
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
         <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH7" t="n">
         <v>5.3</v>
       </c>
-      <c r="BH7" t="n">
-        <v>5</v>
-      </c>
       <c r="BI7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,50 +2307,50 @@
         <v>7.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS7" t="n">
         <v>6.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BX7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="G8" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="I8" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -2399,7 +2399,7 @@
         <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -2411,61 +2411,61 @@
         <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
         <v>5.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AB8" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
         <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AH8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI8" t="n">
         <v>70</v>
@@ -2480,16 +2480,16 @@
         <v>700</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN8" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
         <v>5.1</v>
@@ -2498,25 +2498,25 @@
         <v>7.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AY8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ8" t="n">
         <v>29</v>
@@ -2525,43 +2525,43 @@
         <v>55</v>
       </c>
       <c r="BB8" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF8" t="n">
         <v>17</v>
       </c>
-      <c r="BC8" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>17</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>15</v>
-      </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ8" t="n">
-        <v>70</v>
+        <v>13.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BO8" t="n">
         <v>6.2</v>
@@ -2570,41 +2570,41 @@
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BV8" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.05</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
         <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P9" t="n">
         <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
         <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y9" t="n">
         <v>9</v>
       </c>
-      <c r="Y9" t="n">
-        <v>15.5</v>
-      </c>
       <c r="Z9" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="n">
         <v>9</v>
@@ -2707,13 +2707,13 @@
         <v>6.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG9" t="n">
         <v>14.5</v>
@@ -2722,55 +2722,55 @@
         <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AL9" t="n">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AN9" t="n">
         <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
         <v>34</v>
       </c>
       <c r="AX9" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ9" t="n">
         <v>11.5</v>
@@ -2788,22 +2788,22 @@
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BF9" t="n">
         <v>40</v>
       </c>
       <c r="BG9" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK9" t="n">
         <v>6</v>
@@ -2812,53 +2812,53 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.7</v>
+        <v>9.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.62</v>
+        <v>8.6</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.66</v>
+        <v>8.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -2889,97 +2889,97 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="K10" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
         <v>1.75</v>
       </c>
       <c r="P10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.33</v>
       </c>
       <c r="W10" t="n">
         <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -2997,67 +2997,67 @@
         <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.8</v>
+        <v>46</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK10" t="n">
         <v>6.6</v>
@@ -3066,16 +3066,16 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO10" t="n">
         <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
         <v>8.800000000000001</v>
@@ -3084,10 +3084,10 @@
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU10" t="n">
         <v>5.3</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>2.88</v>
       </c>
       <c r="G11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -3161,7 +3161,7 @@
         <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -3170,25 +3170,25 @@
         <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
         <v>1.51</v>
@@ -3197,31 +3197,31 @@
         <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
       </c>
       <c r="Z11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF11" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>21</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
@@ -3230,13 +3230,13 @@
         <v>17.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
         <v>50</v>
@@ -3248,10 +3248,10 @@
         <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.4</v>
@@ -3260,64 +3260,64 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
         <v>16.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="BB11" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BC11" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE11" t="n">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BG11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK11" t="n">
         <v>5.4</v>
       </c>
       <c r="BL11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM11" t="n">
         <v>10.5</v>
@@ -3329,44 +3329,44 @@
         <v>5</v>
       </c>
       <c r="BP11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR11" t="n">
         <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT11" t="n">
         <v>5.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA11" t="n">
         <v>8.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 08:57:22</t>
+          <t>2026-06-02 11:04:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
         <v>6.2</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X2" t="n">
+      <c r="AH2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>29</v>
       </c>
-      <c r="Y2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="BF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG2" t="n">
         <v>23</v>
       </c>
-      <c r="AG2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM2" t="n">
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL2" t="n">
         <v>200</v>
       </c>
-      <c r="AN2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="BM2" t="n">
+        <v>34</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX2" t="n">
         <v>11</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>24</v>
-      </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>15.5</v>
+        <v>190</v>
       </c>
       <c r="CA2" t="n">
-        <v>6.6</v>
+        <v>29</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1111,178 +1111,178 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>2.46</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="X3" t="n">
         <v>28</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="Z3" t="n">
+        <v>960</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR3" t="n">
         <v>24</v>
       </c>
-      <c r="AA3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AS3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AI3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>17</v>
-      </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BB3" t="n">
-        <v>29</v>
+        <v>3.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>3.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="BJ3" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.8</v>
+        <v>1.09</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1291,50 +1291,50 @@
         <v>55</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>1.09</v>
       </c>
       <c r="BP3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>1.09</v>
       </c>
       <c r="BR3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>1.09</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5</v>
+        <v>1.09</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>1.09</v>
       </c>
       <c r="BX3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="BZ3" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="G4" t="n">
         <v>1.19</v>
@@ -1374,13 +1374,13 @@
         <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="J4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>1.13</v>
@@ -1389,28 +1389,28 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O4" t="n">
         <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="R4" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.05</v>
@@ -1419,55 +1419,55 @@
         <v>6.2</v>
       </c>
       <c r="X4" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="Y4" t="n">
         <v>950</v>
       </c>
       <c r="Z4" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AC4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AD4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AE4" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AK4" t="n">
         <v>14.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1485,55 +1485,55 @@
         <v>4.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA4" t="n">
         <v>5.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
         <v>5.4</v>
@@ -1545,22 +1545,22 @@
         <v>65</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BS4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BT4" t="n">
         <v>21</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
         <v>22</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="O5" t="n">
         <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1709,7 +1709,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK5" t="n">
         <v>500</v>
@@ -1727,7 +1727,7 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.2</v>
@@ -1739,10 +1739,10 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AV5" t="n">
         <v>4.2</v>
@@ -1751,31 +1751,31 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BE5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.19</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>4.2</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.32</v>
@@ -1897,55 +1897,55 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
         <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
         <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1960,16 +1960,16 @@
         <v>18.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1978,91 +1978,91 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD6" t="n">
         <v>20</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>13</v>
-      </c>
       <c r="BE6" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BF6" t="n">
         <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="BH6" t="n">
         <v>4.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2071,22 +2071,22 @@
         <v>9</v>
       </c>
       <c r="BT6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
         <v>11</v>
       </c>
-      <c r="BU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.26</v>
@@ -2151,163 +2151,163 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.47</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.53</v>
-      </c>
       <c r="U7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W7" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="Y7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>14.5</v>
+        <v>120</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
         <v>44</v>
       </c>
       <c r="AK7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM7" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AN7" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF7" t="n">
+      <c r="BH7" t="n">
         <v>5</v>
       </c>
-      <c r="BG7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BI7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO7" t="n">
         <v>4.1</v>
@@ -2319,38 +2319,38 @@
         <v>6</v>
       </c>
       <c r="BR7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BX7" t="n">
         <v>24</v>
       </c>
-      <c r="BS7" t="n">
+      <c r="BY7" t="n">
         <v>6.4</v>
       </c>
-      <c r="BT7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="CA7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="I8" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -2411,67 +2411,67 @@
         <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
         <v>2.66</v>
       </c>
       <c r="R8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V8" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
         <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AF8" t="n">
         <v>500</v>
       </c>
       <c r="AG8" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>900</v>
+        <v>390</v>
       </c>
       <c r="AK8" t="n">
         <v>700</v>
@@ -2480,13 +2480,13 @@
         <v>700</v>
       </c>
       <c r="AM8" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AP8" t="n">
         <v>8</v>
@@ -2495,31 +2495,31 @@
         <v>5.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX8" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AY8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BA8" t="n">
         <v>55</v>
@@ -2528,83 +2528,83 @@
         <v>29</v>
       </c>
       <c r="BC8" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="BD8" t="n">
-        <v>60</v>
+        <v>17.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BI8" t="n">
         <v>2.52</v>
       </c>
       <c r="BJ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>13.5</v>
       </c>
-      <c r="BK8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BT8" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2635,70 +2635,70 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I9" t="n">
         <v>3.1</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
         <v>3.05</v>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="M9" t="n">
         <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
         <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z9" t="n">
         <v>19</v>
       </c>
       <c r="AA9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
         <v>9</v>
@@ -2710,16 +2710,16 @@
         <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
         <v>17.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>75</v>
@@ -2728,22 +2728,22 @@
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AL9" t="n">
         <v>75</v>
       </c>
       <c r="AM9" t="n">
-        <v>450</v>
+        <v>180</v>
       </c>
       <c r="AN9" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
         <v>8</v>
@@ -2752,7 +2752,7 @@
         <v>15.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2764,7 +2764,7 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX9" t="n">
         <v>15</v>
@@ -2773,92 +2773,92 @@
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BC9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="BF9" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BG9" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ9" t="n">
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BN9" t="n">
         <v>6</v>
       </c>
       <c r="BO9" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
         <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="L10" t="n">
         <v>1.75</v>
@@ -2913,16 +2913,16 @@
         <v>1.16</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
@@ -2931,22 +2931,22 @@
         <v>7.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z10" t="n">
         <v>110</v>
@@ -2955,13 +2955,13 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC10" t="n">
         <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
@@ -2970,16 +2970,16 @@
         <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
         <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
         <v>500</v>
@@ -3000,13 +3000,13 @@
         <v>6.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT10" t="n">
         <v>5.9</v>
@@ -3015,10 +3015,10 @@
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -3027,28 +3027,28 @@
         <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE10" t="n">
         <v>46</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10" t="n">
         <v>2.44</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>2.98</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I11" t="n">
         <v>2.98</v>
@@ -3158,49 +3158,49 @@
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.51</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
         <v>19</v>
@@ -3209,7 +3209,7 @@
         <v>48</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
@@ -3218,40 +3218,40 @@
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG11" t="n">
         <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
         <v>46</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
         <v>36</v>
       </c>
       <c r="AO11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.4</v>
@@ -3263,10 +3263,10 @@
         <v>38</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
         <v>11.5</v>
@@ -3281,7 +3281,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
         <v>44</v>
@@ -3296,16 +3296,16 @@
         <v>42</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>44</v>
       </c>
       <c r="BF11" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG11" t="n">
         <v>28</v>
       </c>
-      <c r="BG11" t="n">
-        <v>22</v>
-      </c>
       <c r="BH11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI11" t="n">
         <v>2.6</v>
@@ -3314,59 +3314,59 @@
         <v>10.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP11" t="n">
         <v>24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR11" t="n">
         <v>40</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV11" t="n">
         <v>24</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX11" t="n">
         <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ11" t="n">
         <v>36</v>
       </c>
       <c r="CA11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-02 11:04:34</t>
+          <t>2026-06-02 13:11:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,33 +843,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SV Grodig</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TSV Neumarkt</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1.02</v>
+        <v>280</v>
       </c>
       <c r="H2" t="n">
-        <v>280</v>
+        <v>3.35</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>1.98</v>
       </c>
       <c r="K2" t="n">
         <v>150</v>
@@ -887,16 +887,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -926,7 +926,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -950,73 +950,73 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.52</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.5</v>
+        <v>250</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.5</v>
+        <v>250</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.5</v>
+        <v>250</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="AU2" t="n">
-        <v>15.5</v>
+        <v>2.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>15.5</v>
+        <v>1.71</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>1.72</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="AY2" t="n">
-        <v>15.5</v>
+        <v>1.59</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>2.64</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.75</v>
+        <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.44</v>
+        <v>60</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SK Austria Klagenfurt Amateure</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atus Ferlach</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.06</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.08</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>42</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>2.12</v>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>2.16</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,16 +1141,16 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>12.5</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1180,97 +1180,97 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ3" t="n">
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.49</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP3" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>2.82</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AY3" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.36</v>
+        <v>55</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,54 +1351,54 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rosengard</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Angelholms</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7</v>
+        <v>3.95</v>
       </c>
       <c r="I4" t="n">
-        <v>1.71</v>
+        <v>4.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.74</v>
       </c>
       <c r="P4" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
         <v>1.13</v>
@@ -1407,195 +1407,195 @@
         <v>7.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>2.44</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>8</v>
       </c>
-      <c r="AA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>230</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>80</v>
+        <v>9.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BC4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
-        <v>75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="BF4" t="n">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="BG4" t="n">
-        <v>60</v>
+        <v>9.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,1260 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Assyriska FF</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enkopings SK</t>
+          <t>Atletico Nacional Medell</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.08</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA5" t="n">
         <v>46</v>
       </c>
-      <c r="I5" t="n">
-        <v>210</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>19</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>12</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.94</v>
+        <v>38</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AP5" t="n">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>220</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>220</v>
+        <v>15.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>220</v>
+        <v>38</v>
       </c>
       <c r="AT5" t="n">
-        <v>220</v>
+        <v>9.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>220</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>220</v>
+        <v>11.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="AX5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BK5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN5" t="n">
         <v>5.9</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BO5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BE5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>48</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-02 15:18:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Algerian Ligue 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>USM Alger</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Belouizdad</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>70</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>11</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:18:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Italian Serie C</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>16:15:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Union Brescia</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ascoli</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>240</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>48</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>46</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>950</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>55</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>50</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:18:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Argentinian Primera B Metropolitana</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Deportivo Merlo</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Deportivo Laferrere</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>12</v>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:18:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Junior FC Barranquilla</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medell</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>36</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:18:07</t>
+          <t>2026-06-02 17:24:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,36 +843,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>280</v>
+        <v>950</v>
       </c>
       <c r="H2" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>270</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>150</v>
+        <v>1.82</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -887,16 +887,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -926,22 +926,22 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.78</v>
+        <v>1.84</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>770</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -950,7 +950,7 @@
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.71</v>
+        <v>2.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.59</v>
+        <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BB2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BE2" t="n">
-        <v>95</v>
+        <v>3.85</v>
       </c>
       <c r="BF2" t="n">
-        <v>60</v>
+        <v>3.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>46</v>
+        <v>3.75</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.5</v>
       </c>
-      <c r="I3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>26</v>
+        <v>200</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
-        <v>9.4</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="n">
+        <v>430</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>310</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>510</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC3" t="n">
         <v>55</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>10</v>
-      </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="BE3" t="n">
-        <v>120</v>
+        <v>460</v>
       </c>
       <c r="BF3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>110</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,498 +1351,244 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Atletico Nacional Medell</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Z4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8</v>
-      </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT4" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.5</v>
       </c>
       <c r="AU4" t="n">
         <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC4" t="n">
         <v>30</v>
       </c>
-      <c r="AX4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP4" t="n">
         <v>24</v>
       </c>
-      <c r="BA4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA4" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-02 17:24:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Junior FC Barranquilla</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medell</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>38</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>2026-06-02 17:24:55</t>
+          <t>2026-06-02 19:31:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,14 +1080,14 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,498 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Atletico Nacional Medell</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M3" t="n">
         <v>1.1</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="N3" t="n">
-        <v>1.69</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.34</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>1.22</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF3" t="n">
         <v>34</v>
       </c>
-      <c r="AA3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>430</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>310</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>510</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>160</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>460</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>65</v>
-      </c>
       <c r="BG3" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI3" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BR3" t="n">
         <v>910</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BX3" t="n">
         <v>950</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BZ3" t="n">
-        <v>860</v>
+        <v>960</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-02 19:31:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Junior FC Barranquilla</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medell</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>38</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-02 19:31:39</t>
+          <t>2026-06-02 21:38:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,261 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-02 21:38:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Junior FC Barranquilla</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Atletico Nacional Medell</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>960</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>590</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>910</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>690</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>950</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>960</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>27</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-02 21:38:14</t>
+          <t>2026-06-02 23:44:49</t>
         </is>
       </c>
     </row>
